--- a/AAII_Financials/Yearly/TBVPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TBVPY_YR_FIN.xlsx
@@ -946,10 +946,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8933900</v>
+        <v>8999200</v>
       </c>
       <c r="E17" s="3">
-        <v>9137400</v>
+        <v>9210800</v>
       </c>
       <c r="F17" s="3">
         <v>8022400</v>
@@ -976,10 +976,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1373000</v>
+        <v>1307700</v>
       </c>
       <c r="E18" s="3">
-        <v>1427500</v>
+        <v>1354000</v>
       </c>
       <c r="F18" s="3">
         <v>1133800</v>
@@ -1050,10 +1050,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1688900</v>
+        <v>1623600</v>
       </c>
       <c r="E21" s="3">
-        <v>1836800</v>
+        <v>1763400</v>
       </c>
       <c r="F21" s="3">
         <v>1480600</v>
